--- a/data/trans_orig/P1414-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1414-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de fibromialgia en 2012</t>
+          <t>Población con diagnóstico de fibromialgia en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4832</t>
+          <t>4833</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>4086</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14387</t>
+          <t>16589</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4711</t>
+          <t>4950</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17142</t>
+          <t>16195</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>289906</t>
+          <t>289905</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>272858</t>
+          <t>270656</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>283237</t>
+          <t>283159</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>564841</t>
+          <t>565788</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>577272</t>
+          <t>577033</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4776</t>
+          <t>5217</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6741</t>
+          <t>6464</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22601</t>
+          <t>21952</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7303</t>
+          <t>7267</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23951</t>
+          <t>23810</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>500751</t>
+          <t>500310</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>501164</t>
+          <t>501813</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>517024</t>
+          <t>517301</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1005341</t>
+          <t>1005482</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1021989</t>
+          <t>1022025</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1942</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11010</t>
+          <t>11311</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1965</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11101</t>
+          <t>11559</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>322102</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>324046</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>330010</t>
+          <t>329709</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>339078</t>
+          <t>339073</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>653965</t>
+          <t>653507</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>663101</t>
+          <t>663115</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,71%</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6006</t>
+          <t>6297</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5865</t>
+          <t>5849</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>18494</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6076</t>
+          <t>6741</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20192</t>
+          <t>19758</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>367976</t>
+          <t>367685</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>370770</t>
+          <t>370457</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>383086</t>
+          <t>383102</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>742741</t>
+          <t>743175</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>756857</t>
+          <t>756192</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2071</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2991</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13763</t>
+          <t>14487</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2943</t>
+          <t>2624</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14928</t>
+          <t>14570</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>210547</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>212618</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>205828</t>
+          <t>205104</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>217023</t>
+          <t>216600</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>417281</t>
+          <t>417639</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>429266</t>
+          <t>429585</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>988</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8909</t>
+          <t>7996</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>992</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8149</t>
+          <t>8035</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>271974</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>273981</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>269187</t>
+          <t>270100</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>277102</t>
+          <t>277108</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>543928</t>
+          <t>544042</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>551078</t>
+          <t>551085</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7261</t>
+          <t>7389</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5107</t>
+          <t>4909</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19046</t>
+          <t>18778</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>6118</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>20368</t>
+          <t>20643</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>655527</t>
+          <t>655399</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>674807</t>
+          <t>675075</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>688746</t>
+          <t>688944</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1336273</t>
+          <t>1335998</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1350477</t>
+          <t>1350523</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6584</t>
+          <t>7434</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>25328</t>
+          <t>25438</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>49441</t>
+          <t>50058</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>27996</t>
+          <t>26886</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>53084</t>
+          <t>53502</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>772514</t>
+          <t>771664</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>772170</t>
+          <t>771553</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>796283</t>
+          <t>796173</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1547625</t>
+          <t>1547207</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1572713</t>
+          <t>1573823</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,32%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3099</t>
+          <t>3156</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14165</t>
+          <t>14751</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>74546</t>
+          <t>74465</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>113080</t>
+          <t>113465</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>83082</t>
+          <t>81633</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>125830</t>
+          <t>122298</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3412614</t>
+          <t>3412028</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3423680</t>
+          <t>3423623</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3441052</t>
+          <t>3440667</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3479586</t>
+          <t>3479667</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6855081</t>
+          <t>6858613</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6897829</t>
+          <t>6899278</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -3860,7 +3860,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de fibromialgia en 2016</t>
+          <t>Población con diagnóstico de fibromialgia en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7189</t>
+          <t>6556</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6748</t>
+          <t>6030</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20324</t>
+          <t>20187</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7896</t>
+          <t>8262</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22835</t>
+          <t>23552</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>286572</t>
+          <t>287205</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>268379</t>
+          <t>268516</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>281955</t>
+          <t>282673</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>559629</t>
+          <t>558912</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>574568</t>
+          <t>574202</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -4403,7 +4403,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4832</t>
+          <t>5907</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8424</t>
+          <t>8956</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24048</t>
+          <t>24755</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9809</t>
+          <t>8921</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26087</t>
+          <t>25267</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>497743</t>
+          <t>496668</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>499036</t>
+          <t>498329</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>514660</t>
+          <t>514128</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>999572</t>
+          <t>1000392</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1015850</t>
+          <t>1016738</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1820</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1794</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9911</t>
+          <t>10724</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>1704</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10921</t>
+          <t>10545</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>316745</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>318565</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>326398</t>
+          <t>325585</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>334515</t>
+          <t>334439</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>643953</t>
+          <t>644329</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>653177</t>
+          <t>653170</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4883</t>
+          <t>4808</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4150</t>
+          <t>4185</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16650</t>
+          <t>16934</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4352</t>
+          <t>4148</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18536</t>
+          <t>17601</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>365081</t>
+          <t>365156</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>370633</t>
+          <t>370349</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>383133</t>
+          <t>383098</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>738711</t>
+          <t>739646</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>752895</t>
+          <t>753099</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7720</t>
+          <t>6861</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7211</t>
+          <t>7237</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21501</t>
+          <t>20948</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9159</t>
+          <t>9296</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25429</t>
+          <t>25483</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>203501</t>
+          <t>204360</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>197086</t>
+          <t>197639</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>211376</t>
+          <t>211350</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>404379</t>
+          <t>404325</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>420649</t>
+          <t>420512</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1942</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2103</t>
+          <t>2223</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12831</t>
+          <t>12897</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2130</t>
+          <t>3041</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12812</t>
+          <t>13300</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>261181</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>263123</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>260284</t>
+          <t>260218</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>271012</t>
+          <t>270892</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>523426</t>
+          <t>522938</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>534108</t>
+          <t>533197</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,43%</t>
         </is>
       </c>
     </row>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6124</t>
+          <t>5982</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6203</t>
+          <t>6479</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20229</t>
+          <t>21116</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6892</t>
+          <t>6642</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22473</t>
+          <t>22248</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>650434</t>
+          <t>650576</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>671065</t>
+          <t>670178</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>685091</t>
+          <t>684815</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1325379</t>
+          <t>1325604</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1340960</t>
+          <t>1341210</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2596</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14298</t>
+          <t>14869</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>37506</t>
+          <t>38918</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>68394</t>
+          <t>68131</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>44828</t>
+          <t>45617</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>79137</t>
+          <t>77461</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>764285</t>
+          <t>763714</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>775980</t>
+          <t>775987</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>757773</t>
+          <t>758036</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>788661</t>
+          <t>787249</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1525613</t>
+          <t>1527289</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1559922</t>
+          <t>1559133</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,16%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8184</t>
+          <t>7736</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>23990</t>
+          <t>24968</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>104227</t>
+          <t>103445</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>150014</t>
+          <t>148355</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>117905</t>
+          <t>117704</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>165636</t>
+          <t>165178</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3370360</t>
+          <t>3369382</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3386166</t>
+          <t>3386614</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3394528</t>
+          <t>3396187</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3440315</t>
+          <t>3441097</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6773256</t>
+          <t>6773714</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6820987</t>
+          <t>6821188</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,7 +6997,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7183,7 +7183,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de fibromialgia en 2023</t>
+          <t>Población con diagnóstico de fibromialgia en 2023 (tasa de respuesta: 99,61%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7383,7 +7383,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8200</t>
+          <t>7830</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17993</t>
+          <t>17510</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8337</t>
+          <t>8302</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18155</t>
+          <t>18794</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -7491,7 +7491,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>306613</t>
+          <t>307441</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>271642</t>
+          <t>272125</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>281435</t>
+          <t>281805</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>582922</t>
+          <t>582283</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>592740</t>
+          <t>592775</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,62%</t>
         </is>
       </c>
     </row>
@@ -7721,12 +7721,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2600</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7736,12 +7736,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13741</t>
+          <t>13895</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27309</t>
+          <t>26870</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13759</t>
+          <t>13461</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28163</t>
+          <t>27788</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -7834,12 +7834,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>514793</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>482994</t>
+          <t>483433</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>496562</t>
+          <t>496408</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7899,17 +7899,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1008068</t>
+          <t>1008069</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>999532</t>
+          <t>999908</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1013936</t>
+          <t>1014235</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -8012,17 +8012,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1027695</t>
+          <t>1027696</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1027695</t>
+          <t>1027696</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1027695</t>
+          <t>1027696</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8069,7 +8069,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4516</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2189</t>
+          <t>2263</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8542</t>
+          <t>9027</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8114,12 +8114,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2793</t>
+          <t>2617</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10665</t>
+          <t>10115</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -8177,7 +8177,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>311534</t>
+          <t>311017</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8192,7 +8192,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>340586</t>
+          <t>340101</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>346939</t>
+          <t>346865</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8227,12 +8227,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>654513</t>
+          <t>655063</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>662385</t>
+          <t>662561</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8262,12 +8262,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -8407,12 +8407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>585</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12627</t>
+          <t>10687</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8442,12 +8442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4284</t>
+          <t>4206</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14466</t>
+          <t>14371</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8457,12 +8457,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7024</t>
+          <t>7282</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20941</t>
+          <t>21330</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -8520,12 +8520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>299348</t>
+          <t>301288</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>311382</t>
+          <t>311390</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>461252</t>
+          <t>461347</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>471434</t>
+          <t>471512</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8570,12 +8570,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8585,17 +8585,17 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>775392</t>
+          <t>775391</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>766752</t>
+          <t>766362</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>780669</t>
+          <t>780410</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -8698,17 +8698,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>787693</t>
+          <t>787692</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>787693</t>
+          <t>787692</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>787693</t>
+          <t>787692</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2599</t>
+          <t>2678</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8785,12 +8785,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7564</t>
+          <t>7791</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15619</t>
+          <t>15944</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8800,12 +8800,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8820,12 +8820,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8447</t>
+          <t>8416</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16577</t>
+          <t>16752</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -8863,7 +8863,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>175622</t>
+          <t>175543</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8878,7 +8878,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8898,12 +8898,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>191743</t>
+          <t>191418</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>199798</t>
+          <t>199571</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8913,12 +8913,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8933,12 +8933,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>369006</t>
+          <t>368831</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>377136</t>
+          <t>377167</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,82%</t>
         </is>
       </c>
     </row>
@@ -9093,12 +9093,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>468</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5518</t>
+          <t>5429</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5360</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13752</t>
+          <t>13670</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9143,12 +9143,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6953</t>
+          <t>6617</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16978</t>
+          <t>16434</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -9206,12 +9206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264118</t>
+          <t>264207</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>269174</t>
+          <t>269168</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9241,12 +9241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>242056</t>
+          <t>242138</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>250448</t>
+          <t>250537</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9256,12 +9256,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>508466</t>
+          <t>509010</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>518491</t>
+          <t>518827</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -9436,12 +9436,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1764</t>
+          <t>1780</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>10326</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9471,12 +9471,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14140</t>
+          <t>13686</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42949</t>
+          <t>43910</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20836</t>
+          <t>21316</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>45979</t>
+          <t>47427</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -9549,12 +9549,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>608915</t>
+          <t>609177</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>617739</t>
+          <t>617723</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9584,12 +9584,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>802171</t>
+          <t>801210</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>830980</t>
+          <t>831434</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9599,12 +9599,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1418643</t>
+          <t>1417195</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1443786</t>
+          <t>1443306</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9065</t>
+          <t>8077</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>34362</t>
+          <t>34738</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>55036</t>
+          <t>55974</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>28535</t>
+          <t>28023</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>59692</t>
+          <t>60613</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -9892,7 +9892,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>919655</t>
+          <t>920643</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>657867</t>
+          <t>656929</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>678541</t>
+          <t>678165</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1581931</t>
+          <t>1581010</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1613088</t>
+          <t>1613600</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,29%</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8432</t>
+          <t>8274</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>24006</t>
+          <t>24721</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>111809</t>
+          <t>112384</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>161825</t>
+          <t>161418</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,12 +10172,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>128277</t>
+          <t>129157</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>175852</t>
+          <t>176545</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3428935</t>
+          <t>3428220</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3444509</t>
+          <t>3444667</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3484150</t>
+          <t>3484557</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3534166</t>
+          <t>3533591</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6923064</t>
+          <t>6922371</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6970639</t>
+          <t>6969759</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,18%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1414-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1414-Provincia-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4833</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4086</t>
+          <t>3971</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16589</t>
+          <t>16098</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4950</t>
+          <t>4972</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16195</t>
+          <t>16594</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>289905</t>
+          <t>289453</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>270656</t>
+          <t>271147</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>283159</t>
+          <t>283274</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>565788</t>
+          <t>565389</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>577033</t>
+          <t>577011</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5217</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6464</t>
+          <t>6462</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21952</t>
+          <t>21939</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7267</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23810</t>
+          <t>23346</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>500310</t>
+          <t>500327</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>501813</t>
+          <t>501826</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>517301</t>
+          <t>517303</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1005482</t>
+          <t>1005946</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1022025</t>
+          <t>1021862</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11311</t>
+          <t>11114</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11559</t>
+          <t>11016</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>329709</t>
+          <t>329906</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>339073</t>
+          <t>339070</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>653507</t>
+          <t>654050</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>663115</t>
+          <t>663120</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6297</t>
+          <t>5780</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5849</t>
+          <t>5117</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18494</t>
+          <t>18357</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6741</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19758</t>
+          <t>20311</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>367685</t>
+          <t>368202</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>370457</t>
+          <t>370594</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>383102</t>
+          <t>383834</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>743175</t>
+          <t>742622</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>756192</t>
+          <t>756263</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2991</t>
+          <t>2767</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14487</t>
+          <t>14585</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>2730</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14570</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>205104</t>
+          <t>205006</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>216600</t>
+          <t>216824</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>417639</t>
+          <t>418528</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>429585</t>
+          <t>429479</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>990</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7996</t>
+          <t>8125</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>996</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8035</t>
+          <t>8575</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>270100</t>
+          <t>269971</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>277108</t>
+          <t>277106</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>544042</t>
+          <t>543502</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>551085</t>
+          <t>551081</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7389</t>
+          <t>7248</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>4258</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18778</t>
+          <t>18040</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6118</t>
+          <t>6837</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>20643</t>
+          <t>21982</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>655399</t>
+          <t>655540</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>675075</t>
+          <t>675813</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>688944</t>
+          <t>689595</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1335998</t>
+          <t>1334659</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1350523</t>
+          <t>1349804</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7434</t>
+          <t>7623</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>25438</t>
+          <t>25535</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>50058</t>
+          <t>50674</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>26886</t>
+          <t>26791</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>53502</t>
+          <t>50638</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>771664</t>
+          <t>771475</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>771553</t>
+          <t>770937</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>796173</t>
+          <t>796076</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1547207</t>
+          <t>1550071</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1573823</t>
+          <t>1573918</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,33%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3156</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14751</t>
+          <t>14843</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>74465</t>
+          <t>74492</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>113465</t>
+          <t>112317</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>81633</t>
+          <t>80983</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>122298</t>
+          <t>122212</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3412028</t>
+          <t>3411936</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3423623</t>
+          <t>3423678</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3440667</t>
+          <t>3441815</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3479667</t>
+          <t>3479640</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6858613</t>
+          <t>6858699</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6899278</t>
+          <t>6899928</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6556</t>
+          <t>7055</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6030</t>
+          <t>6725</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20187</t>
+          <t>19590</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8262</t>
+          <t>7777</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23552</t>
+          <t>22915</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>287205</t>
+          <t>286706</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>268516</t>
+          <t>269113</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>282673</t>
+          <t>281978</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>558912</t>
+          <t>559549</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>574202</t>
+          <t>574687</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -4403,7 +4403,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5907</t>
+          <t>5368</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8956</t>
+          <t>8314</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24755</t>
+          <t>24173</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8921</t>
+          <t>9628</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25267</t>
+          <t>25192</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>496668</t>
+          <t>497207</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>498329</t>
+          <t>498911</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>514128</t>
+          <t>514770</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1000392</t>
+          <t>1000467</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1016738</t>
+          <t>1016031</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>1682</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10724</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>1727</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10545</t>
+          <t>10229</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>325585</t>
+          <t>326166</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>334439</t>
+          <t>334627</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>644329</t>
+          <t>644645</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>653170</t>
+          <t>653147</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4808</t>
+          <t>4867</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4185</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16934</t>
+          <t>16949</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4148</t>
+          <t>4691</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17601</t>
+          <t>17119</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>365156</t>
+          <t>365097</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>370349</t>
+          <t>370334</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>383098</t>
+          <t>383123</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>739646</t>
+          <t>740128</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>753099</t>
+          <t>752556</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6861</t>
+          <t>6774</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7237</t>
+          <t>7931</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20948</t>
+          <t>21329</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9296</t>
+          <t>8196</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25483</t>
+          <t>24576</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>204360</t>
+          <t>204447</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>197639</t>
+          <t>197258</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>211350</t>
+          <t>210656</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>404325</t>
+          <t>405232</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>420512</t>
+          <t>421612</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>98,09%</t>
         </is>
       </c>
     </row>
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2223</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12897</t>
+          <t>12529</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3041</t>
+          <t>2312</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13300</t>
+          <t>13112</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>260218</t>
+          <t>260586</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>270892</t>
+          <t>271015</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>522938</t>
+          <t>523126</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>533197</t>
+          <t>533926</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6479</t>
+          <t>6561</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21116</t>
+          <t>21873</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6642</t>
+          <t>7481</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22248</t>
+          <t>22721</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>670178</t>
+          <t>669421</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>684815</t>
+          <t>684733</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1325604</t>
+          <t>1325131</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1341210</t>
+          <t>1340371</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2596</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14869</t>
+          <t>14272</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>38918</t>
+          <t>39219</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>68131</t>
+          <t>67942</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6506,47 +6506,47 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
+          <t>4,75%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>8,22%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>59198</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>43670</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>75577</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>3,69%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>2,72%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
           <t>4,71%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>8,25%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>59198</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>45617</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>77461</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>763714</t>
+          <t>764311</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>775987</t>
+          <t>776433</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>758036</t>
+          <t>758225</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>787249</t>
+          <t>786948</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,47 +6619,47 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
+          <t>95,25%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>1453</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>1545552</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>1529173</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>1561080</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>96,31%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>95,29%</t>
         </is>
       </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1453</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1545552</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>1527289</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>1559133</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>96,31%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>95,17%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,28%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7736</t>
+          <t>7964</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>24968</t>
+          <t>23343</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>103445</t>
+          <t>104683</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>148355</t>
+          <t>152413</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>117704</t>
+          <t>118219</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>165178</t>
+          <t>163638</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3369382</t>
+          <t>3371007</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3386614</t>
+          <t>3386386</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3396187</t>
+          <t>3392129</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3441097</t>
+          <t>3439859</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6773714</t>
+          <t>6775254</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6821188</t>
+          <t>6820673</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,7 +6997,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>668</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>3213</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7408,32 +7408,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>12138</t>
+          <t>12838</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7830</t>
+          <t>8396</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17510</t>
+          <t>18219</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7443,32 +7443,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>12863</t>
+          <t>13506</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8302</t>
+          <t>9140</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18794</t>
+          <t>19754</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -7486,27 +7486,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>310718</t>
+          <t>318177</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>307441</t>
+          <t>315632</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7521,32 +7521,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>277497</t>
+          <t>303223</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>272125</t>
+          <t>297842</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>281805</t>
+          <t>307665</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7556,32 +7556,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>588214</t>
+          <t>621400</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>582283</t>
+          <t>615152</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>592775</t>
+          <t>625766</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -7599,17 +7599,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7634,17 +7634,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7669,17 +7669,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7751,32 +7751,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19627</t>
+          <t>19961</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13895</t>
+          <t>13737</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26870</t>
+          <t>28483</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7786,32 +7786,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>19627</t>
+          <t>19961</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13461</t>
+          <t>13594</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27788</t>
+          <t>27680</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -7829,7 +7829,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -7864,32 +7864,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>490676</t>
+          <t>521310</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>483433</t>
+          <t>512788</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>496408</t>
+          <t>527534</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7899,32 +7899,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1008069</t>
+          <t>1050970</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>999908</t>
+          <t>1043251</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1014235</t>
+          <t>1057337</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -7942,17 +7942,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7977,17 +7977,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>510303</t>
+          <t>541271</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>510303</t>
+          <t>541271</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>510303</t>
+          <t>541271</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8012,17 +8012,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1027696</t>
+          <t>1070931</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1027696</t>
+          <t>1070931</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1027696</t>
+          <t>1070931</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8059,7 +8059,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>868</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>4812</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8094,32 +8094,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4682</t>
+          <t>5344</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2263</t>
+          <t>2465</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9027</t>
+          <t>10150</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8129,32 +8129,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>5577</t>
+          <t>6212</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2617</t>
+          <t>2972</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10115</t>
+          <t>11543</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -8172,27 +8172,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>315156</t>
+          <t>315125</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>311017</t>
+          <t>311181</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8207,32 +8207,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>344446</t>
+          <t>351037</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>340101</t>
+          <t>346231</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>346865</t>
+          <t>353916</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8242,32 +8242,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>659601</t>
+          <t>666163</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>655063</t>
+          <t>660832</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>662561</t>
+          <t>669403</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -8285,17 +8285,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8355,17 +8355,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8402,32 +8402,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3624</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>600</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10687</t>
+          <t>13076</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8437,32 +8437,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8677</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4206</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14371</t>
+          <t>14867</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8472,27 +8472,27 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>12301</t>
+          <t>12967</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7282</t>
+          <t>7885</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21330</t>
+          <t>21553</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -8515,32 +8515,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>308351</t>
+          <t>368790</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>301288</t>
+          <t>359482</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>311390</t>
+          <t>371958</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8550,32 +8550,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>467041</t>
+          <t>412762</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>461347</t>
+          <t>407094</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>471512</t>
+          <t>416283</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8585,22 +8585,22 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>775391</t>
+          <t>781553</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>766362</t>
+          <t>772967</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>780410</t>
+          <t>786635</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,01%</t>
         </is>
       </c>
     </row>
@@ -8628,17 +8628,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>311975</t>
+          <t>372558</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>311975</t>
+          <t>372558</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>311975</t>
+          <t>372558</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8663,17 +8663,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8698,17 +8698,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>787692</t>
+          <t>794520</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>787692</t>
+          <t>794520</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>787692</t>
+          <t>794520</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>521</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2678</t>
+          <t>2745</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8780,32 +8780,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11459</t>
+          <t>11930</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7791</t>
+          <t>8168</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15944</t>
+          <t>16832</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8815,32 +8815,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>11972</t>
+          <t>12451</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8416</t>
+          <t>8834</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16752</t>
+          <t>18125</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -8858,27 +8858,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>177708</t>
+          <t>204563</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>175543</t>
+          <t>202339</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>178221</t>
+          <t>205084</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8893,32 +8893,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>195903</t>
+          <t>213890</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>191418</t>
+          <t>208988</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>199571</t>
+          <t>217652</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8928,32 +8928,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>373611</t>
+          <t>418453</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>368831</t>
+          <t>412779</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>377167</t>
+          <t>422070</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,95%</t>
         </is>
       </c>
     </row>
@@ -8971,17 +8971,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178221</t>
+          <t>205084</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178221</t>
+          <t>205084</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178221</t>
+          <t>205084</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9006,17 +9006,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>207362</t>
+          <t>225820</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>207362</t>
+          <t>225820</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>207362</t>
+          <t>225820</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9041,17 +9041,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>385583</t>
+          <t>430904</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>385583</t>
+          <t>430904</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>385583</t>
+          <t>430904</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9088,22 +9088,22 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1755</t>
+          <t>1732</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>452</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5429</t>
+          <t>5273</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9123,32 +9123,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8805</t>
+          <t>8863</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>5665</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13670</t>
+          <t>14118</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9158,32 +9158,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>10560</t>
+          <t>10595</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6617</t>
+          <t>6414</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16434</t>
+          <t>15800</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -9201,27 +9201,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>267881</t>
+          <t>268975</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264207</t>
+          <t>265434</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>269168</t>
+          <t>270255</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9236,32 +9236,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>247003</t>
+          <t>253656</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>242138</t>
+          <t>248401</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>250537</t>
+          <t>256854</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9271,32 +9271,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>514884</t>
+          <t>522631</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>509010</t>
+          <t>517426</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>518827</t>
+          <t>526812</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -9314,17 +9314,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9349,17 +9349,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>255808</t>
+          <t>262519</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>255808</t>
+          <t>262519</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>255808</t>
+          <t>262519</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9384,17 +9384,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>525444</t>
+          <t>533226</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>525444</t>
+          <t>533226</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>525444</t>
+          <t>533226</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9431,32 +9431,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>5091</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1780</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10326</t>
+          <t>10975</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9466,67 +9466,67 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>29912</t>
+          <t>35887</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13686</t>
+          <t>27575</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43910</t>
+          <t>46187</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
+          <t>4,69%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>3,61%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>6,04%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>40979</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>32103</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>52399</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>2,77%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>3,54%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>5,2%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>34727</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>21316</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>47427</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -9544,32 +9544,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>614688</t>
+          <t>709233</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>609177</t>
+          <t>703349</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>617723</t>
+          <t>712587</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9579,67 +9579,67 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>815208</t>
+          <t>728539</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>801210</t>
+          <t>718239</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>831434</t>
+          <t>736851</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
+          <t>95,31%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>93,96%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>96,39%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>1486</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>1437771</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>1426351</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>1446647</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>97,23%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>96,46%</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>94,8%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>98,38%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1486</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1429895</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>1417195</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1443306</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>97,63%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>96,76%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>
@@ -9657,17 +9657,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>619503</t>
+          <t>714324</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>619503</t>
+          <t>714324</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>619503</t>
+          <t>714324</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9692,17 +9692,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>845120</t>
+          <t>764426</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>845120</t>
+          <t>764426</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>845120</t>
+          <t>764426</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9727,17 +9727,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1464622</t>
+          <t>1478750</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1464622</t>
+          <t>1478750</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1464622</t>
+          <t>1478750</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>2119</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -9784,12 +9784,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8077</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9809,32 +9809,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>44311</t>
+          <t>50919</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>34738</t>
+          <t>41280</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>55974</t>
+          <t>64026</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9844,32 +9844,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>46288</t>
+          <t>53038</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>28023</t>
+          <t>42830</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>60613</t>
+          <t>67963</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -9887,27 +9887,27 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>926743</t>
+          <t>795953</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>920643</t>
+          <t>790827</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9922,32 +9922,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>668592</t>
+          <t>776901</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>656929</t>
+          <t>763794</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>678165</t>
+          <t>786540</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9957,32 +9957,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1595335</t>
+          <t>1572854</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1581010</t>
+          <t>1557929</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1613600</t>
+          <t>1583062</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -10000,17 +10000,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10035,17 +10035,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>712903</t>
+          <t>827820</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>712903</t>
+          <t>827820</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>712903</t>
+          <t>827820</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10070,17 +10070,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1641623</t>
+          <t>1625892</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1641623</t>
+          <t>1625892</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1641623</t>
+          <t>1625892</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10117,32 +10117,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>14305</t>
+          <t>14767</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8274</t>
+          <t>8751</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>24721</t>
+          <t>24926</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10152,32 +10152,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>139611</t>
+          <t>154942</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>112384</t>
+          <t>137214</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>161418</t>
+          <t>175174</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10187,32 +10187,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>153915</t>
+          <t>169709</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>129157</t>
+          <t>149484</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>176545</t>
+          <t>190076</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -10230,32 +10230,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3438636</t>
+          <t>3510476</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3428220</t>
+          <t>3500317</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3444667</t>
+          <t>3516492</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10265,32 +10265,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3506364</t>
+          <t>3561318</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3484557</t>
+          <t>3541086</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3533591</t>
+          <t>3579046</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10300,32 +10300,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6945001</t>
+          <t>7071794</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6922371</t>
+          <t>7051427</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6969759</t>
+          <t>7092019</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -10343,17 +10343,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3452941</t>
+          <t>3525243</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3452941</t>
+          <t>3525243</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3452941</t>
+          <t>3525243</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10378,17 +10378,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3645975</t>
+          <t>3716260</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3645975</t>
+          <t>3716260</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3645975</t>
+          <t>3716260</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10413,17 +10413,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7098916</t>
+          <t>7241503</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7098916</t>
+          <t>7241503</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7098916</t>
+          <t>7241503</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
